--- a/Tableau_synthese_NicolasLUONG.xlsx
+++ b/Tableau_synthese_NicolasLUONG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B62815D-4950-47F2-8A9A-599D04FBEFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92192C21-D5DD-4F73-B6DB-B947D4495031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -153,9 +153,6 @@
     <t>Haute disponibilité - WordPress</t>
   </si>
   <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
     <t>Ferme RDS à double broker - UPD</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
   </si>
   <si>
     <t>Virtualisation 2SRV ProxMox + PBS</t>
-  </si>
-  <si>
-    <t>AD + GPO</t>
   </si>
   <si>
     <t>Veille Technologique</t>
@@ -182,6 +176,21 @@
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>https://proxiasa.github.io/projet-ha-wordpress.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                        https://proxiasa.github.io/projet-infra-complete.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                    https://proxiasa.github.io/projet-rds-aintranet.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                    https://proxiasa.github.io/projet-rds-mairie.html</t>
   </si>
 </sst>
 </file>
@@ -191,7 +200,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -259,6 +268,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -268,7 +284,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -654,12 +670,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -709,15 +735,60 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -751,54 +822,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1115,56 +1146,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="19"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="37" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="32"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="13" t="s">
         <v>8</v>
       </c>
@@ -1176,22 +1207,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="30"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="41" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1214,9 +1245,9 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="39" t="s">
+      <c r="A7" s="34"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="17" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -1231,7 +1262,7 @@
       <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="18" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1271,16 +1302,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1321,8 +1352,8 @@
       <c r="A9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>32</v>
+      <c r="B9" s="21">
+        <v>2025</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>28</v>
@@ -1337,7 +1368,7 @@
       <c r="G9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="41"/>
+      <c r="H9" s="19"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1378,7 +1409,9 @@
       <c r="A10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="20">
+        <v>2025</v>
+      </c>
       <c r="C10" s="15" t="s">
         <v>28</v>
       </c>
@@ -1388,7 +1421,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="15"/>
-      <c r="H10" s="41"/>
+      <c r="H10" s="19"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1429,7 +1462,9 @@
       <c r="A11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="42"/>
+      <c r="B11" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="C11" s="15" t="s">
         <v>28</v>
       </c>
@@ -1443,10 +1478,12 @@
       <c r="G11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11"/>
+      <c r="H11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="47" t="s">
+        <v>42</v>
+      </c>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
@@ -1486,7 +1523,9 @@
       <c r="A12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="42"/>
+      <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15" t="s">
         <v>28</v>
@@ -1496,8 +1535,10 @@
       <c r="G12" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="41"/>
-      <c r="I12"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="46" t="s">
+        <v>41</v>
+      </c>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
@@ -1535,9 +1576,11 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="42"/>
+        <v>34</v>
+      </c>
+      <c r="B13" s="20">
+        <v>2026</v>
+      </c>
       <c r="C13" s="15" t="s">
         <v>28</v>
       </c>
@@ -1549,7 +1592,7 @@
       <c r="G13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="41"/>
+      <c r="H13" s="19"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1588,21 +1631,21 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>28</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="41"/>
+      <c r="F14" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="19" t="s">
+        <v>28</v>
+      </c>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1640,20 +1683,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="42"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="15" t="s">
-        <v>28</v>
-      </c>
+      <c r="F15" s="15"/>
       <c r="G15" s="15"/>
-      <c r="H15" s="41" t="s">
-        <v>28</v>
-      </c>
+      <c r="H15" s="19"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1692,15 +1729,15 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="42"/>
+        <v>39</v>
+      </c>
+      <c r="B16" s="20"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
-      <c r="H16" s="41"/>
+      <c r="H16" s="19"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1739,13 +1776,13 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
-      <c r="B17" s="42"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
-      <c r="H17" s="41"/>
+      <c r="H17" s="19"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1784,13 +1821,13 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
-      <c r="B18" s="42"/>
+      <c r="B18" s="20"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="41"/>
+      <c r="H18" s="19"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1828,16 +1865,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1876,9 +1913,11 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="42"/>
+        <v>32</v>
+      </c>
+      <c r="B20" s="20">
+        <v>2025</v>
+      </c>
       <c r="C20" s="15" t="s">
         <v>28</v>
       </c>
@@ -1892,10 +1931,12 @@
       <c r="G20" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20"/>
+      <c r="H20" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>43</v>
+      </c>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
@@ -1933,9 +1974,11 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="42"/>
+        <v>36</v>
+      </c>
+      <c r="B21" s="20">
+        <v>2025</v>
+      </c>
       <c r="C21" s="15" t="s">
         <v>28</v>
       </c>
@@ -1949,7 +1992,7 @@
       <c r="G21" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="41" t="s">
+      <c r="H21" s="19" t="s">
         <v>28</v>
       </c>
       <c r="I21"/>
@@ -1990,9 +2033,11 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="42"/>
+        <v>37</v>
+      </c>
+      <c r="B22" s="20">
+        <v>2025</v>
+      </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15" t="s">
         <v>28</v>
@@ -2002,7 +2047,7 @@
       <c r="G22" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="19" t="s">
         <v>28</v>
       </c>
       <c r="I22"/>
@@ -2043,13 +2088,13 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
-      <c r="B23" s="42"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
-      <c r="H23" s="41"/>
+      <c r="H23" s="19"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2088,13 +2133,13 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
-      <c r="B24" s="42"/>
+      <c r="B24" s="20"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="41"/>
+      <c r="H24" s="19"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2133,13 +2178,13 @@
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
-      <c r="B25" s="42"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
-      <c r="H25" s="41"/>
+      <c r="H25" s="19"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2178,13 +2223,13 @@
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
-      <c r="B26" s="42"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
-      <c r="H26" s="41"/>
+      <c r="H26" s="19"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2222,16 +2267,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="25"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2270,9 +2315,11 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2026</v>
+      </c>
       <c r="C28" s="15" t="s">
         <v>28</v>
       </c>
@@ -2286,10 +2333,12 @@
       <c r="G28" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28"/>
+      <c r="H28" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>44</v>
+      </c>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
@@ -2327,9 +2376,11 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="B29" s="9">
+        <v>2026</v>
+      </c>
       <c r="C29" s="15" t="s">
         <v>28</v>
       </c>
@@ -2343,7 +2394,7 @@
       <c r="G29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="41" t="s">
+      <c r="H29" s="19" t="s">
         <v>28</v>
       </c>
       <c r="I29"/>
@@ -2384,9 +2435,11 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="B30" s="9">
+        <v>2026</v>
+      </c>
       <c r="C30" s="15"/>
       <c r="D30" s="15" t="s">
         <v>28</v>
@@ -2396,7 +2449,7 @@
       <c r="G30" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="41" t="s">
+      <c r="H30" s="19" t="s">
         <v>28</v>
       </c>
       <c r="I30"/>
@@ -2443,7 +2496,7 @@
       <c r="E31" s="15"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
-      <c r="H31" s="41"/>
+      <c r="H31" s="19"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2488,7 +2541,7 @@
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
-      <c r="H32" s="41"/>
+      <c r="H32" s="19"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2533,7 +2586,7 @@
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
-      <c r="H33" s="41"/>
+      <c r="H33" s="19"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2573,12 +2626,12 @@
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
       <c r="B34" s="12"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="45"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="23"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2708,11 +2761,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2720,11 +2768,22 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I12" r:id="rId1" xr:uid="{65D3020B-F942-46B2-BC16-6CC21584628A}"/>
+    <hyperlink ref="I11" r:id="rId2" display="https://proxiasa.github.io/projet-infra-complete.html" xr:uid="{4D97B3FE-3EE1-45A9-9F58-A0A4C09421E4}"/>
+    <hyperlink ref="I20" r:id="rId3" display="https://proxiasa.github.io/projet-rds-aintranet.html" xr:uid="{F66F1802-21FC-4D95-8669-B0C7F5307670}"/>
+    <hyperlink ref="I28" r:id="rId4" display="https://proxiasa.github.io/projet-rds-mairie.html" xr:uid="{AF5B4740-0D98-44F7-B129-F3EB792C3D6B}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>